--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486425_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486425_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8454</v>
+        <v>6.0643</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5942</v>
+        <v>4.9057</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2511</v>
+        <v>1.1587</v>
       </c>
       <c r="G2" t="n">
         <v>4.2729</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>1.92</v>
+        <v>1.1389</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5863</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3337</v>
+        <v>0.2412</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6109</v>
+        <v>2.4985</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7232</v>
+        <v>1.3505</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8877</v>
+        <v>1.148</v>
       </c>
       <c r="G3" t="n">
         <v>1.0803</v>
@@ -688,13 +688,13 @@
         <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1832</v>
+        <v>1.0707</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3869</v>
+        <v>0.2403</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5701</v>
+        <v>0.8304</v>
       </c>
       <c r="V3" t="n">
         <v>0.5649999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3982</v>
+        <v>2.194</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4868</v>
+        <v>1.375</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9115</v>
+        <v>0.819</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0436</v>
@@ -766,13 +766,13 @@
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0944</v>
+        <v>0.8902</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7691</v>
+        <v>0.6573</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3253</v>
+        <v>0.2328</v>
       </c>
       <c r="V4" t="n">
         <v>1.13</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0453</v>
+        <v>2.1823</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1809</v>
+        <v>1.3179</v>
       </c>
       <c r="F5" t="n">
         <v>0.8643</v>
@@ -844,10 +844,10 @@
         <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>0.149</v>
+        <v>0.286</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0961</v>
+        <v>0.2331</v>
       </c>
       <c r="U5" t="n">
         <v>0.0529</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.215</v>
+        <v>1.692</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6215</v>
+        <v>1.9135</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4064</v>
+        <v>-0.2215</v>
       </c>
       <c r="G6" t="n">
         <v>1.1939</v>
@@ -922,13 +922,13 @@
         <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2192</v>
+        <v>0.2578</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2379</v>
+        <v>0.0541</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0187</v>
+        <v>0.2037</v>
       </c>
       <c r="V6" t="n">
         <v>-1.4997</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5101</v>
+        <v>1.4709</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6625</v>
+        <v>-0.01</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1727</v>
+        <v>1.4809</v>
       </c>
       <c r="G7" t="n">
         <v>-3.1093</v>
@@ -1000,13 +1000,13 @@
         <v>2.3926</v>
       </c>
       <c r="S7" t="n">
-        <v>0.012</v>
+        <v>0.9728</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2452</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2331</v>
+        <v>0.0751</v>
       </c>
       <c r="V7" t="n">
         <v>3.3899</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4875</v>
+        <v>0.5975</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9033</v>
+        <v>1.705</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4157</v>
+        <v>-1.1075</v>
       </c>
       <c r="G8" t="n">
         <v>0.6145</v>
@@ -1078,13 +1078,13 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1694</v>
+        <v>-0.0595</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7487</v>
+        <v>0.5504</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9181</v>
+        <v>-0.6099</v>
       </c>
       <c r="V8" t="n">
         <v>1.13</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>D. SARAIVA SEIXAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7442</v>
+        <v>-1.709</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3968</v>
+        <v>-0.4464</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.141</v>
+        <v>-1.2626</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5767</v>
+        <v>-0.9675</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9607</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.616</v>
+        <v>-1.965</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6443</v>
+        <v>0.0828</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6443</v>
+        <v>1.4964</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.4136</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9324</v>
+        <v>-1.0504</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3164</v>
+        <v>-0.4989</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.616</v>
+        <v>-0.5514</v>
       </c>
       <c r="P9" t="n">
         <v>0.6525</v>
@@ -1156,28 +1156,28 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0598</v>
+        <v>0.1057</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3461</v>
+        <v>0.2103</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4059</v>
+        <v>-0.1046</v>
       </c>
       <c r="V9" t="n">
+        <v>-1.4997</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.7395</v>
+      </c>
+      <c r="X9" t="n">
         <v>-0.7602</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.695</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-2.4552</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. SARAIVA SEIXAS</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1128</v>
+        <v>-1.8809</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8502</v>
+        <v>1.1985</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2626</v>
+        <v>-3.0793</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9675</v>
+        <v>-1.5767</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9975000000000001</v>
+        <v>-0.9607</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.965</v>
+        <v>-0.616</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0828</v>
+        <v>-0.6443</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4964</v>
+        <v>-0.6443</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4136</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0504</v>
+        <v>-0.9324</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4989</v>
+        <v>-0.3164</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5514</v>
+        <v>-0.616</v>
       </c>
       <c r="P10" t="n">
         <v>0.6525</v>
@@ -1234,22 +1234,22 @@
         <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.298</v>
+        <v>-0.1965</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1935</v>
+        <v>0.1478</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1046</v>
+        <v>-0.3443</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4997</v>
+        <v>-0.7602</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7395</v>
+        <v>1.695</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7602</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.6253</v>
+        <v>-6.4519</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5745</v>
+        <v>-5.4627</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0508</v>
+        <v>-0.9892</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1988</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0344</v>
+        <v>-0.861</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4795</v>
+        <v>-0.3677</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.4933</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8695</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.6301</v>
+        <v>6.6577</v>
       </c>
       <c r="E12" t="n">
-        <v>6.819500000000001</v>
+        <v>7.847</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1892</v>
+        <v>-1.189199999999999</v>
       </c>
       <c r="G12" t="n">
         <v>0.1598000000000002</v>
@@ -1390,13 +1390,13 @@
         <v>13.0504</v>
       </c>
       <c r="S12" t="n">
-        <v>2.577800000000001</v>
+        <v>3.605099999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4937</v>
+        <v>3.521</v>
       </c>
       <c r="U12" t="n">
-        <v>0.08410000000000006</v>
+        <v>0.08400000000000013</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3696000000000004</v>
@@ -1405,7 +1405,7 @@
         <v>7.5815</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.9512</v>
+        <v>-7.951199999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.3141</v>
+        <v>6.8555</v>
       </c>
       <c r="E13" t="n">
-        <v>7.9201</v>
+        <v>7.1378</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.606</v>
+        <v>-0.2822</v>
       </c>
       <c r="G13" t="n">
         <v>4.4751</v>
@@ -1468,13 +1468,13 @@
         <v>1.0875</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1664</v>
+        <v>0.7078</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1272</v>
+        <v>0.3449</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0392</v>
+        <v>0.3629</v>
       </c>
       <c r="V13" t="n">
         <v>1.8902</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. TAMBA VILLEN</t>
+          <t>K. LARSEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7146</v>
+        <v>2.0216</v>
       </c>
       <c r="E14" t="n">
-        <v>0.868</v>
+        <v>2.5831</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8466</v>
+        <v>-0.5615</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4081</v>
+        <v>-0.3292</v>
       </c>
       <c r="H14" t="n">
-        <v>0.961</v>
+        <v>1.8797</v>
       </c>
       <c r="I14" t="n">
-        <v>0.447</v>
+        <v>-2.2089</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9125</v>
+        <v>1.5884</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9125</v>
+        <v>3.8419</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-2.2535</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4956</v>
+        <v>-1.9176</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0486</v>
+        <v>-1.9622</v>
       </c>
       <c r="O14" t="n">
-        <v>0.447</v>
+        <v>0.0446</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R14" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9591</v>
+        <v>-0.6264</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0431</v>
+        <v>-0.5251</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.1013</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>3.1947</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.8249</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. LARSEN</t>
+          <t>I. TAMBA VILLEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.581</v>
+        <v>1.5592</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4714</v>
+        <v>0.5327</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8904</v>
+        <v>1.0264</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3292</v>
+        <v>1.4081</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8797</v>
+        <v>0.961</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.2089</v>
+        <v>0.447</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5884</v>
+        <v>0.9125</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8419</v>
+        <v>0.9125</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.2535</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9176</v>
+        <v>0.4956</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.9622</v>
+        <v>0.0486</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0446</v>
+        <v>0.447</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2175</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.067</v>
+        <v>0.8036</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6369</v>
+        <v>0.7078</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4301</v>
+        <v>0.0958</v>
       </c>
       <c r="V15" t="n">
-        <v>3.1947</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8249</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3194</v>
+        <v>0.8525</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0304</v>
+        <v>0.0814</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3498</v>
+        <v>0.7711</v>
       </c>
       <c r="G16" t="n">
         <v>1.1073</v>
@@ -1702,13 +1702,13 @@
         <v>0.435</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2228</v>
+        <v>-0.6898</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.411</v>
+        <v>-0.2992</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8119</v>
+        <v>-0.3906</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1518</v>
+        <v>0.3274</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3128</v>
+        <v>0.6481</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4646</v>
+        <v>-0.3207</v>
       </c>
       <c r="G17" t="n">
         <v>-0.895</v>
@@ -1780,13 +1780,13 @@
         <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0907</v>
+        <v>0.5699</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4554</v>
+        <v>-0.1202</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5462</v>
+        <v>0.6901</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. RICHARDSON</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6685</v>
+        <v>-1.5066</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2218</v>
+        <v>-2.6677</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4468</v>
+        <v>1.1611</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9361</v>
+        <v>-2.7146</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3222</v>
+        <v>-2.8071</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2582</v>
+        <v>0.0924</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2323</v>
+        <v>-2.9273</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4745</v>
+        <v>-2.1257</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7068</v>
+        <v>-0.8016</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7038</v>
+        <v>0.2127</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1523</v>
+        <v>-0.6814</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5514</v>
+        <v>0.8941</v>
       </c>
       <c r="P18" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R18" t="n">
         <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>0.267</v>
+        <v>0.2064</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2499</v>
+        <v>0.4771</v>
       </c>
       <c r="U18" t="n">
-        <v>0.517</v>
+        <v>-0.2707</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8695</v>
+        <v>0.3491</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.13</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0333</v>
+        <v>-1.5675</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8912</v>
+        <v>-1.2115</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8579</v>
+        <v>-0.356</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.7146</v>
+        <v>0.7163</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.8071</v>
+        <v>-0.067</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0924</v>
+        <v>0.7833</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.9273</v>
+        <v>0.0382</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.1257</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8016</v>
+        <v>0.0382</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2127</v>
+        <v>0.6781</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6814</v>
+        <v>-0.067</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8941</v>
+        <v>0.7451</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6525</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3203</v>
+        <v>-0.3061</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2536</v>
+        <v>-0.1622</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5738</v>
+        <v>-0.1439</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3491</v>
+        <v>-1.3252</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3491</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>M. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0698</v>
+        <v>-1.738</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3233</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-2.6013</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7163</v>
+        <v>1.1624</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.067</v>
+        <v>1.0859</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7833</v>
+        <v>0.0765</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0382</v>
+        <v>3.4266</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2.9476</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0382</v>
+        <v>0.4789</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6781</v>
+        <v>-2.2642</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.067</v>
+        <v>-1.8617</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7451</v>
+        <v>-0.4024</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6525</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8084</v>
+        <v>-0.6829</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.274</v>
+        <v>-0.3881</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5344</v>
+        <v>-0.2947</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1339</v>
+        <v>-1.8732</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3716</v>
+        <v>-2.2598</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2377</v>
+        <v>0.3867</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6766</v>
@@ -2092,13 +2092,13 @@
         <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6525</v>
+        <v>-0.3918</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.08890000000000001</v>
+        <v>0.0228</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5636</v>
+        <v>-0.4146</v>
       </c>
       <c r="V21" t="n">
         <v>0.1952</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. TORRES CUEVAS</t>
+          <t>T. RICHARDSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4251</v>
+        <v>-1.9626</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7516</v>
+        <v>-1.11</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1768</v>
+        <v>-0.8526</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1624</v>
+        <v>-0.9361</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0859</v>
+        <v>0.3222</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0765</v>
+        <v>-1.2582</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4266</v>
+        <v>-0.2323</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9476</v>
+        <v>0.4745</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4789</v>
+        <v>-0.7068</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.2642</v>
+        <v>-0.7038</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.8617</v>
+        <v>-0.1523</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4024</v>
+        <v>-0.5514</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.37</v>
+        <v>-0.027</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4999</v>
+        <v>-0.1382</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8702</v>
+        <v>0.1111</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.13</v>
+        <v>-1.8695</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X22" t="n">
         <v>-1.13</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9014</v>
+        <v>-2.8628</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2602</v>
+        <v>-1.0367</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6412</v>
+        <v>-1.8261</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5626</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7912</v>
+        <v>0.8298</v>
       </c>
       <c r="T23" t="n">
-        <v>0.161</v>
+        <v>0.3845</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6302</v>
+        <v>0.4452</v>
       </c>
       <c r="V23" t="n">
         <v>-1.695</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5146</v>
+        <v>-3.1563</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0361</v>
+        <v>-2.3714</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4785</v>
+        <v>-0.7849</v>
       </c>
       <c r="G24" t="n">
         <v>-1.2127</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4521</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0529</v>
+        <v>-0.3881</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3992</v>
+        <v>0.2944</v>
       </c>
       <c r="V24" t="n">
         <v>0.7602</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.9693</v>
+        <v>-3.0508</v>
       </c>
       <c r="E25" t="n">
-        <v>1.189299999999999</v>
+        <v>1.189400000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.158800000000001</v>
+        <v>-4.240000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-0.4575999999999996</v>
       </c>
       <c r="H25" t="n">
-        <v>-4.282800000000001</v>
+        <v>-4.2828</v>
       </c>
       <c r="I25" t="n">
         <v>3.8249</v>
@@ -2404,16 +2404,16 @@
         <v>9.787499999999998</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.6187</v>
+        <v>0.2998000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.08399999999999994</v>
+        <v>-0.08400000000000007</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.5346</v>
+        <v>0.3837</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3696999999999999</v>
+        <v>0.3697000000000004</v>
       </c>
       <c r="W25" t="n">
         <v>7.9512</v>
